--- a/output/roomself_excel/13736.xlsx
+++ b/output/roomself_excel/13736.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>290127</v>
+        <v>102944</v>
       </c>
       <c r="D2" t="n">
-        <v>5072</v>
+        <v>2676</v>
       </c>
       <c r="E2" t="n">
-        <v>699</v>
+        <v>390</v>
       </c>
       <c r="F2" t="n">
-        <v>693</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>102944</v>
+        <v>39618</v>
       </c>
       <c r="D3" t="n">
-        <v>2676</v>
+        <v>1596</v>
       </c>
       <c r="E3" t="n">
-        <v>633</v>
+        <v>213</v>
       </c>
       <c r="F3" t="n">
-        <v>390</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>39618</v>
+        <v>290127</v>
       </c>
       <c r="D4" t="n">
-        <v>1596</v>
+        <v>5072</v>
       </c>
       <c r="E4" t="n">
-        <v>213</v>
+        <v>699</v>
       </c>
       <c r="F4" t="n">
-        <v>80</v>
+        <v>693</v>
       </c>
     </row>
     <row r="5">

--- a/output/roomself_excel/13736.xlsx
+++ b/output/roomself_excel/13736.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,92 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_5</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_6</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_6</t>
         </is>
       </c>
     </row>
@@ -475,12 +555,48 @@
       <c r="D2" t="n">
         <v>2676</v>
       </c>
-      <c r="E2" t="n">
-        <v>390</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>380</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>332</v>
+      </c>
+      <c r="J2" t="n">
+        <v>53</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>337</v>
+      </c>
+      <c r="M2" t="n">
+        <v>20</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +613,32 @@
       <c r="D3" t="n">
         <v>1596</v>
       </c>
-      <c r="E3" t="n">
-        <v>213</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>80</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="G3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +655,71 @@
       <c r="D4" t="n">
         <v>5072</v>
       </c>
-      <c r="E4" t="n">
-        <v>699</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>693</v>
+        <v>650</v>
+      </c>
+      <c r="G4" t="n">
+        <v>53</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>200</v>
+      </c>
+      <c r="J4" t="n">
+        <v>27</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>234</v>
+      </c>
+      <c r="M4" t="n">
+        <v>41</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>384</v>
+      </c>
+      <c r="P4" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>38</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>209</v>
+      </c>
+      <c r="V4" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +737,32 @@
       <c r="D5" t="n">
         <v>1228</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>137</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>27</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/13736.xlsx
+++ b/output/roomself_excel/13736.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:AP5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +537,106 @@
       <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ExtWallWidth_6</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_4</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_4</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_4</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_4</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_5</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_5</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_5</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_5</t>
         </is>
       </c>
     </row>
@@ -597,6 +697,50 @@
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>257</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>153</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>53</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -639,6 +783,26 @@
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -719,6 +883,86 @@
         <v>209</v>
       </c>
       <c r="V4" t="n">
+        <v>22</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>332</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>181</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>41</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>93</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>82</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AO4" t="n">
+        <v>92</v>
+      </c>
+      <c r="AP4" t="n">
         <v>22</v>
       </c>
     </row>
@@ -763,6 +1007,26 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
